--- a/data/all_exchanges_futures_margin.xlsx
+++ b/data/all_exchanges_futures_margin.xlsx
@@ -15,6 +15,7 @@
     <sheet name="HYPEUSDT" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="XRPUSDT" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="MSTRUSDT" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SOXLUSDT" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20188,4 +20189,2358 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>交易所</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>檔位</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>倉位分級</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>最大槓桿</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>維持保證金率</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>維持金額(USDT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>40x</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1,625</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>4,125</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>15x</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>12,425</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>45,825</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>8,000,000</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>5x</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>295,825</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>20,000,000</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>495,825</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1,329,825</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>5,494,825</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>200,000,000</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>30,494,825</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>4.00%</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>25,000,000</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>60.00%</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>150,000</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>1,040</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>400,000</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>1,470</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>1,870</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>600,000</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>2.38%</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2,420</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>3,140</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>2.63%</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>4,180</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1,500,000</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>5,680</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>8,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2,500,000</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>11,880</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>3,000,000</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>16,880</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>3,500,000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>24,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>4,000,000</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>33,880</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>4,500,000</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>46,680</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>63,780</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>6,000,000</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>86,280</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>7,000,000</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>5.56%</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>119,880</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>200x</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>11,500</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>53,000</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>9.52</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>9.09</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>4.00%</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>8.70</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>5.50%</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>7.41</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>6.50%</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>10,800</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>7.00%</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>7.50%</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>14,400</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>8.50%</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>16,800</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>9.50%</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>19,200</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>10.50%</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>20,400</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>11.00%</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>21,600</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>11.50%</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>22,800</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>12.00%</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>SOXL</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>24,000</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/all_exchanges_futures_margin.xlsx
+++ b/data/all_exchanges_futures_margin.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2216,1221 +2216,1961 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>2,600,000</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>3,200,000</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>3,020</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>3,800,000</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>4,400,000</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>5,820</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>8,460</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>5,600,000</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>15,460</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>8,500,000</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>20,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>46,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>14,000,000</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>66,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>20,000,000</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>28,000,000</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>160,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>38,000,000</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>452,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>55,000,000</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>502,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>60,000,000</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>777,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>65,000,000</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>837,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>70,000,000</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>967,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>75,000,000</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>1,107,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>80,000,000</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>1,482,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>500x</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F66" s="9" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>200x</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>100x</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F68" s="9" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>50x</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>1,750</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>20x</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F70" s="9" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D71" s="9" t="inlineStr">
         <is>
           <t>1,900</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>10x</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D72" s="11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F72" s="11" t="inlineStr">
         <is>
           <t>0.40%</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E73" s="11" t="inlineStr">
         <is>
           <t>66.66</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D74" s="11" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E74" s="11" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F74" s="11" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>1.25%</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D76" s="11" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E76" s="11" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>1.75%</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E77" s="11" t="inlineStr">
         <is>
           <t>28.57</t>
         </is>
       </c>
-      <c r="F57" s="11" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>2.25%</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D78" s="11" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="F58" s="11" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>2.75%</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D79" s="11" t="inlineStr">
         <is>
           <t>1,200</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E79" s="11" t="inlineStr">
         <is>
           <t>22.22</t>
         </is>
       </c>
-      <c r="F59" s="11" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>3.25%</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D80" s="11" t="inlineStr">
         <is>
           <t>1,400</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>3.75%</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr">
         <is>
           <t>1,600</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E81" s="11" t="inlineStr">
         <is>
           <t>18.18</t>
         </is>
       </c>
-      <c r="F61" s="11" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>4.25%</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>1,800</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>16.66</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>4.75%</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>15.38</t>
         </is>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>5.25%</t>
         </is>
       </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>2,200</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>14.28</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>5.75%</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>2,400</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>6.25%</t>
         </is>
       </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D86" s="11" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>12.50</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>6.75%</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D87" s="11" t="inlineStr">
         <is>
           <t>2,800</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr">
+      <c r="E87" s="11" t="inlineStr">
         <is>
           <t>11.76</t>
         </is>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>7.25%</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D88" s="11" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="E88" s="11" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="F68" s="11" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>7.75%</t>
         </is>
       </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr">
+      <c r="E89" s="11" t="inlineStr">
         <is>
           <t>10.52</t>
         </is>
       </c>
-      <c r="F69" s="11" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>8.25%</t>
         </is>
       </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D90" s="11" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="F70" s="11" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>8.75%</t>
         </is>
       </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="D91" s="11" t="inlineStr">
         <is>
           <t>3,600</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr">
+      <c r="E91" s="11" t="inlineStr">
         <is>
           <t>9.52</t>
         </is>
       </c>
-      <c r="F71" s="11" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>9.25%</t>
         </is>
       </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>檔位 1</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
         <is>
           <t>2,000,000</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr">
+      <c r="E92" s="15" t="inlineStr">
         <is>
           <t>100x</t>
         </is>
       </c>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="F92" s="15" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="G72" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>檔位 2</t>
         </is>
       </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>12,000,000</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="E93" s="15" t="inlineStr">
         <is>
           <t>50x</t>
         </is>
       </c>
-      <c r="F73" s="15" t="inlineStr">
+      <c r="F93" s="15" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="G73" s="15" t="inlineStr">
+      <c r="G93" s="15" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="14" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>檔位 3</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>100,000,000</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E94" s="15" t="inlineStr">
         <is>
           <t>20x</t>
         </is>
       </c>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="F94" s="15" t="inlineStr">
         <is>
           <t>2.50%</t>
         </is>
       </c>
-      <c r="G74" s="15" t="inlineStr">
+      <c r="G94" s="15" t="inlineStr">
         <is>
           <t>190,000</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>檔位 4</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>200,000,000</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="E95" s="15" t="inlineStr">
         <is>
           <t>10x</t>
         </is>
       </c>
-      <c r="F75" s="15" t="inlineStr">
+      <c r="F95" s="15" t="inlineStr">
         <is>
           <t>5.00%</t>
         </is>
       </c>
-      <c r="G75" s="15" t="inlineStr">
+      <c r="G95" s="15" t="inlineStr">
         <is>
           <t>2,690,000</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="14" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>檔位 5</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
         <is>
           <t>500,000,000</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr">
         <is>
           <t>5x</t>
         </is>
       </c>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="F96" s="15" t="inlineStr">
         <is>
           <t>10.00%</t>
         </is>
       </c>
-      <c r="G76" s="15" t="inlineStr">
+      <c r="G96" s="15" t="inlineStr">
         <is>
           <t>12,690,000</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>檔位 6</t>
         </is>
       </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
         <is>
           <t>600,000,000</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="E97" s="15" t="inlineStr">
         <is>
           <t>2x</t>
         </is>
       </c>
-      <c r="F77" s="15" t="inlineStr">
+      <c r="F97" s="15" t="inlineStr">
         <is>
           <t>25.00%</t>
         </is>
       </c>
-      <c r="G77" s="15" t="inlineStr">
+      <c r="G97" s="15" t="inlineStr">
         <is>
           <t>87,690,000</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B98" s="14" t="inlineStr">
         <is>
           <t>檔位 7</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>800,000,000</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E98" s="15" t="inlineStr">
         <is>
           <t>1x</t>
         </is>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F98" s="15" t="inlineStr">
         <is>
           <t>50.00%</t>
         </is>
       </c>
-      <c r="G78" s="15" t="inlineStr">
+      <c r="G98" s="15" t="inlineStr">
         <is>
           <t>237,690,000</t>
         </is>

--- a/data/all_exchanges_futures_margin.xlsx
+++ b/data/all_exchanges_futures_margin.xlsx
@@ -547,17 +547,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="94" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,37 +569,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>原始資料</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>檔位</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>單位</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>倉位分級</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>最大槓桿</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>維持保證金率</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>維持金額(USDT)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>原始資料</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>內容</t>
         </is>
       </c>
     </row>
@@ -610,35 +616,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>150x</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>初始保證金 = 倉位價值 / 槓桿</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -648,35 +639,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>800,000</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>維持保證金 = 倉位價值 * 維持保證金比率 - 維持金額</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -686,35 +662,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>3,000,000</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>75x</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>了解更多</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -724,35 +685,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>12,000,000</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>50x</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>*最大 倍槓桿 U 本位合約包括：:</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -762,35 +708,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>70,000,000</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>2.00%</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>132,000</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>請注意，在異常價格波動和極端市場行情下，幣安會採取額外的措施來維護市場穩定，包括但不限於：</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -800,35 +731,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>100,000,000</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>482,000</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>1. 調整最高槓桿倍數</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -838,35 +754,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>230,000,000</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>10x</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2,982,000</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2. 調整不同層級的倉位限制</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -876,187 +777,176 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>480,000,000</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>5x</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>14,482,000</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>3. 調整不同層級的維持保證金比率</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>600,000,000</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>4x</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>12.50%</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>26,482,000</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>檔位 1</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>320,000</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>150x</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>0.1000%</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>800,000,000</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>3x</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>15.00%</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>41,482,000</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>檔位 2</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>1,500,000</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>125x</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>0.2500%</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>1,200,000,000</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2x</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>25.00%</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>121,482,000</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>檔位 3</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>7,500,000</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>125x</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>0.4000%</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>2,730</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>1,800,000,000</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>50.00%</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>421,482,000</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>檔位 4</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>8,500,000</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>62x</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>47,730</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -1066,35 +956,36 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>檔位 1</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr"/>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>320,000</t>
+          <t>檔位 5</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>150x</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>0.1000%</t>
+          <t>62x</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr"/>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>73,230</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -1104,35 +995,36 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>檔位 2</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr"/>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>檔位 6</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>125x</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>0.2500%</t>
+          <t>41x</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr"/>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>93,230</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -1142,35 +1034,36 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>檔位 3</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr"/>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>7,500,000</t>
+          <t>檔位 7</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>125x</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>0.4000%</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>2,730</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr"/>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>107,230</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -1180,35 +1073,36 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>檔位 4</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr"/>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>檔位 8</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>62x</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>47,730</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr"/>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>187,230</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -1218,35 +1112,36 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>檔位 5</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr"/>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>檔位 9</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>62x</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>73,230</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr"/>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>327,230</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -1256,35 +1151,36 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>檔位 6</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr"/>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>14,000,000</t>
+          <t>檔位 10</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>41x</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>93,230</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr"/>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>479,230</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -1294,35 +1190,36 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>檔位 7</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr"/>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>20,000,000</t>
+          <t>檔位 11</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
+          <t>55,000,000</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
           <t>25x</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>1.60%</t>
-        </is>
-      </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>107,230</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>529,230</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -1332,35 +1229,36 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>檔位 8</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr"/>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>檔位 12</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
+          <t>60,000,000</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
           <t>25x</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>187,230</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr"/>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>804,230</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -1370,35 +1268,36 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>檔位 9</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>檔位 13</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
+          <t>65,000,000</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
           <t>25x</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>327,230</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr"/>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>864,230</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -1408,35 +1307,36 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>檔位 10</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr"/>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>檔位 14</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
+          <t>70,000,000</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
           <t>25x</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>2.90%</t>
-        </is>
-      </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>479,230</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr"/>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>994,230</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -1446,35 +1346,36 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>檔位 11</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr"/>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>55,000,000</t>
+          <t>檔位 15</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>75,000,000</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>529,230</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>1,134,230</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -1484,35 +1385,36 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>檔位 12</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr"/>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>檔位 16</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>80,000,000</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>804,230</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr"/>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>1,509,230</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -1522,35 +1424,36 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>檔位 13</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr"/>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>65,000,000</t>
+          <t>檔位 17</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>230,000,000</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>864,230</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr"/>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>1,909,230</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -1560,35 +1463,36 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>檔位 14</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr"/>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>70,000,000</t>
+          <t>檔位 18</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>600,000,000</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>994,230</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr"/>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>19,159,230</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -1598,35 +1502,36 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>檔位 15</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr"/>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>75,000,000</t>
+          <t>檔位 19</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>1,200,000,000</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3x</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>1,134,230</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr"/>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>94,159,230</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -1636,231 +1541,238 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>檔位 16</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr"/>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>80,000,000</t>
+          <t>檔位 20</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>1,800,000,000</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>1,509,230</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr"/>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>394,159,230</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>檔位 17</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>230,000,000</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>1,909,230</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>檔位	價值 (USDT)	槓桿	檔位維持保證金率</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>檔位 18</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>600,000,000</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>5x</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>12.50%</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>19,159,230</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>暫無數據</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>檔位 19</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>1,200,000,000</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>3x</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>94,159,230</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr"/>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>檔位 20</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>1,800,000,000</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>394,159,230</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr"/>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>2,600,000</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr"/>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>檔位	價值 (--)	槓桿	檔位維持保證金率</t>
-        </is>
-      </c>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>3,200,000</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>3,020</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>暫無數據</t>
-        </is>
-      </c>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>3,800,000</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1870,35 +1782,36 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4,400,000</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr"/>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>5,820</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -1908,35 +1821,36 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>1,200</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr"/>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>8,460</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1946,35 +1860,36 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>3,020</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr"/>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>15,460</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -1984,35 +1899,36 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr"/>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>3,800,000</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>4,300</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr"/>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>20,500</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -2022,35 +1938,36 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>5,820</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>46,000</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -2060,35 +1977,36 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>8,460</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>66,000</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -2098,35 +2016,36 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>15,460</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr"/>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -2136,35 +2055,36 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr"/>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>20,500</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr"/>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>160,000</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2174,35 +2094,36 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr"/>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>46,000</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr"/>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -2212,35 +2133,36 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>14,000,000</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>66,000</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr"/>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>452,000</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -2250,35 +2172,36 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>20,000,000</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>55,000,000</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>80,000</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr"/>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>502,000</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -2288,35 +2211,36 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr"/>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>160,000</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>777,000</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2326,35 +2250,36 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr"/>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>65,000,000</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>300,000</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr"/>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>837,000</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -2364,35 +2289,36 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr"/>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70,000,000</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>452,000</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr"/>
+          <t>3.8%</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>967,000</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2402,35 +2328,36 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>75,000,000</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>55,000,000</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>502,000</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>1,107,000</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -2440,187 +2367,192 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>80,000,000</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>777,000</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr"/>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>1,482,000</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>65,000,000</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>837,000</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr"/>
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr"/>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>500x</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>70,000,000</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>967,000</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr"/>
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr"/>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>200x</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>75,000,000</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>1,107,000</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr"/>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr"/>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>80,000,000</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>1,482,000</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr"/>
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr"/>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2630,14 +2562,10 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C56" s="8" t="inlineStr"/>
       <c r="D56" s="9" t="inlineStr">
         <is>
           <t>5</t>
@@ -2645,20 +2573,25 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>500x</t>
+          <t>1,750</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr"/>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -2668,187 +2601,192 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr"/>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr"/>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr"/>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>66.66</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>200x</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr"/>
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr"/>
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>50x</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>1,750</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>1,900</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>10x</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr"/>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -2858,35 +2796,36 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C62" s="10" t="inlineStr"/>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr"/>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -2896,35 +2835,36 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C63" s="10" t="inlineStr"/>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>66.66</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="11" t="inlineStr"/>
+          <t>2.25%</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -2934,35 +2874,36 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C64" s="10" t="inlineStr"/>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr"/>
+          <t>2.75%</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -2972,35 +2913,36 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C65" s="10" t="inlineStr"/>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr"/>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -3010,35 +2952,36 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C66" s="10" t="inlineStr"/>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr"/>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -3048,35 +2991,36 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C67" s="10" t="inlineStr"/>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="11" t="inlineStr"/>
+          <t>4.25%</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -3086,35 +3030,36 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C68" s="10" t="inlineStr"/>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr"/>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -3124,35 +3069,36 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C69" s="10" t="inlineStr"/>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr"/>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -3162,35 +3108,36 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C70" s="10" t="inlineStr"/>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr"/>
+          <t>5.75%</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -3200,35 +3147,36 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C71" s="10" t="inlineStr"/>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>1,600</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr"/>
+          <t>6.25%</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -3238,35 +3186,36 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C72" s="10" t="inlineStr"/>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="11" t="inlineStr"/>
+          <t>6.75%</t>
+        </is>
+      </c>
+      <c r="H72" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -3276,35 +3225,36 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C73" s="10" t="inlineStr"/>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr"/>
+          <t>7.25%</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -3314,35 +3264,36 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C74" s="10" t="inlineStr"/>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>2,200</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="11" t="inlineStr"/>
+          <t>7.75%</t>
+        </is>
+      </c>
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -3352,35 +3303,36 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C75" s="10" t="inlineStr"/>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="11" t="inlineStr"/>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -3390,35 +3342,36 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C76" s="10" t="inlineStr"/>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>6.75%</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="11" t="inlineStr"/>
+          <t>8.75%</t>
+        </is>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -3428,187 +3381,192 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
           <t>BTC</t>
         </is>
       </c>
+      <c r="C77" s="10" t="inlineStr"/>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>2,800</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr"/>
+          <t>9.25%</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>7.75%</t>
-        </is>
-      </c>
-      <c r="G78" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="11" t="inlineStr"/>
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr"/>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>檔位 1</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>10.52</t>
-        </is>
-      </c>
-      <c r="F79" s="11" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="G79" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr"/>
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr"/>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>檔位 2</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>12,000,000</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="I79" s="15" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>8.75%</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="11" t="inlineStr"/>
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr"/>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>檔位 3</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>190,000</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>9.25%</t>
-        </is>
-      </c>
-      <c r="G81" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="11" t="inlineStr"/>
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr"/>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>檔位 4</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>200,000,000</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>2,690,000</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
@@ -3618,35 +3576,36 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>檔位 1</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr"/>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>檔位 5</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>500,000,000</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="15" t="inlineStr"/>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>12,690,000</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
@@ -3656,35 +3615,36 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>檔位 2</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr"/>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>檔位 6</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>50x</t>
+          <t>600,000,000</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="G83" s="15" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="H83" s="15" t="inlineStr"/>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>87,690,000</t>
+        </is>
+      </c>
+      <c r="I83" s="15" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
@@ -3694,187 +3654,36 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>檔位 3</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr"/>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>檔位 7</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>800,000,000</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
         <is>
-          <t>190,000</t>
-        </is>
-      </c>
-      <c r="H84" s="15" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>檔位 4</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>200,000,000</t>
-        </is>
-      </c>
-      <c r="E85" s="15" t="inlineStr">
-        <is>
-          <t>10x</t>
-        </is>
-      </c>
-      <c r="F85" s="15" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
-      <c r="G85" s="15" t="inlineStr">
-        <is>
-          <t>2,690,000</t>
-        </is>
-      </c>
-      <c r="H85" s="15" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>檔位 5</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>500,000,000</t>
-        </is>
-      </c>
-      <c r="E86" s="15" t="inlineStr">
-        <is>
-          <t>5x</t>
-        </is>
-      </c>
-      <c r="F86" s="15" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="G86" s="15" t="inlineStr">
-        <is>
-          <t>12,690,000</t>
-        </is>
-      </c>
-      <c r="H86" s="15" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>檔位 6</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D87" s="15" t="inlineStr">
-        <is>
-          <t>600,000,000</t>
-        </is>
-      </c>
-      <c r="E87" s="15" t="inlineStr">
-        <is>
-          <t>2x</t>
-        </is>
-      </c>
-      <c r="F87" s="15" t="inlineStr">
-        <is>
-          <t>25.00%</t>
-        </is>
-      </c>
-      <c r="G87" s="15" t="inlineStr">
-        <is>
-          <t>87,690,000</t>
-        </is>
-      </c>
-      <c r="H87" s="15" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>檔位 7</t>
-        </is>
-      </c>
-      <c r="C88" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>800,000,000</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="F88" s="15" t="inlineStr">
-        <is>
           <t>50.00%</t>
         </is>
       </c>
-      <c r="G88" s="15" t="inlineStr">
+      <c r="H84" s="15" t="inlineStr">
         <is>
           <t>237,690,000</t>
         </is>
       </c>
-      <c r="H88" s="15" t="inlineStr"/>
+      <c r="I84" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3887,7 +3696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4381,2405 +4190,3256 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>檔位 1</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>320,000</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>150x</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>0.1000%</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>檔位 2</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>900,000</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>125x</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>0.3300%</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>檔位 3</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>3,000,000</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>125x</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>0.4000%</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>1,366</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>檔位 4</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>3,200,000</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>62x</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>0.7700%</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>12,466</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>檔位 5</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>4,000,000</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>62x</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>0.9100%</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>16,946</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>檔位 6</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>41x</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>20,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>檔位 7</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>8,000,000</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>30,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>檔位 8</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>12,000,000</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>38,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>檔位 9</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>16,000,000</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>1.40%</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>50,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>檔位 10</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>22,000,000</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>1.50%</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>66,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>檔位 11</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>28,000,000</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>176,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>檔位 12</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>32,000,000</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>316,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>檔位 13</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>34,000,000</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>476,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>檔位 14</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>36,000,000</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>578,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>檔位 15</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>38,000,000</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>650,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>檔位 16</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>40,000,000</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>764,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>檔位 17</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>42,000,000</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>3.90%</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>804,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>檔位 18</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>44,000,000</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>930,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>檔位 19</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>46,000,000</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>1,062,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>檔位 20</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>150,000,000</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>1,292,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>檔位 21</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>400,000,000</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>5x</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>12,542,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>檔位 22</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>800,000,000</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>62,542,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>檔位 23</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>1,200,000,000</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>262,542,546</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>0.40%</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>1,000,000</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>5,000,000</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>0.70%</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>15,000,000</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>50,000,000</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>2.00%</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>100,000,000</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>150,000,000</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>6.00%</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>300,000,000</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>12.00%</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>500,000,000</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>15.00%</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>700,000,000</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>20.00%</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>900,000,000</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>30.00%</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Bitget</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>1,200,000,000</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>60.00%</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>2,000,000</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>2,600,000</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>0.56%</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>1,200</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>3,200,000</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>0.63%</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>3,020</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>3,800,000</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>0.67%</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>4,300</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>4,400,000</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>0.71%</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>5,820</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>5,000,000</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>0.77%</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>8,460</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>5,600,000</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>0.91%</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>15,460</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>8,500,000</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>20,500</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>10,000,000</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>1.3%</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>46,000</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>14,000,000</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>1.5%</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>66,000</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>20,000,000</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>1.6%</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>80,000</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>160,000</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>38,000,000</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>50,000,000</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>2.9%</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>452,000</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>55,000,000</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>502,000</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>60,000,000</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>777,000</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>65,000,000</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>3.6%</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>837,000</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>70,000,000</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>3.8%</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>967,000</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>75,000,000</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>1,107,000</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>80,000,000</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>4.5%</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>1,482,000</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>500x</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>1,070</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>200x</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F70" s="9" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D71" s="9" t="inlineStr">
         <is>
           <t>1,500</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>100x</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>8,600</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>50x</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>45,000</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>20x</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>MEXC</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>48,000</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>10x</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F74" s="9" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>0.40%</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D76" s="11" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E76" s="11" t="inlineStr">
         <is>
           <t>66.66</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F76" s="11" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E77" s="11" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F77" s="11" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D78" s="11" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E78" s="11" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F78" s="11" t="inlineStr">
         <is>
           <t>1.25%</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D79" s="11" t="inlineStr">
         <is>
           <t>7,500</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E79" s="11" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F79" s="11" t="inlineStr">
         <is>
           <t>1.75%</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D80" s="11" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>28.57</t>
         </is>
       </c>
-      <c r="F57" s="11" t="inlineStr">
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>2.25%</t>
         </is>
       </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr">
         <is>
           <t>12,500</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E81" s="11" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="F58" s="11" t="inlineStr">
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>2.75%</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>15,000</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>22.22</t>
         </is>
       </c>
-      <c r="F59" s="11" t="inlineStr">
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>3.25%</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
         <is>
           <t>17,500</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>3.75%</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>18.18</t>
         </is>
       </c>
-      <c r="F61" s="11" t="inlineStr">
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>4.25%</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>22,500</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>16.66</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>4.75%</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D86" s="11" t="inlineStr">
         <is>
           <t>25,000</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>15.38</t>
         </is>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>5.25%</t>
         </is>
       </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D87" s="11" t="inlineStr">
         <is>
           <t>27,500</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E87" s="11" t="inlineStr">
         <is>
           <t>14.28</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>5.75%</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D88" s="11" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E88" s="11" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>6.25%</t>
         </is>
       </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>32,500</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E89" s="11" t="inlineStr">
         <is>
           <t>12.50</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F89" s="11" t="inlineStr">
         <is>
           <t>6.75%</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D90" s="11" t="inlineStr">
         <is>
           <t>35,000</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>11.76</t>
         </is>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F90" s="11" t="inlineStr">
         <is>
           <t>7.25%</t>
         </is>
       </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D91" s="11" t="inlineStr">
         <is>
           <t>37,500</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="E91" s="11" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="F68" s="11" t="inlineStr">
+      <c r="F91" s="11" t="inlineStr">
         <is>
           <t>7.75%</t>
         </is>
       </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="D92" s="11" t="inlineStr">
         <is>
           <t>40,000</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr">
+      <c r="E92" s="11" t="inlineStr">
         <is>
           <t>10.52</t>
         </is>
       </c>
-      <c r="F69" s="11" t="inlineStr">
+      <c r="F92" s="11" t="inlineStr">
         <is>
           <t>8.25%</t>
         </is>
       </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="G92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D93" s="11" t="inlineStr">
         <is>
           <t>42,500</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr">
+      <c r="E93" s="11" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="F70" s="11" t="inlineStr">
+      <c r="F93" s="11" t="inlineStr">
         <is>
           <t>8.75%</t>
         </is>
       </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>ETH</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="D94" s="11" t="inlineStr">
         <is>
           <t>45,000</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr">
+      <c r="E94" s="11" t="inlineStr">
         <is>
           <t>9.52</t>
         </is>
       </c>
-      <c r="F71" s="11" t="inlineStr">
+      <c r="F94" s="11" t="inlineStr">
         <is>
           <t>9.25%</t>
         </is>
       </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>檔位 1</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>1,000,000</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr">
+      <c r="E95" s="15" t="inlineStr">
         <is>
           <t>100x</t>
         </is>
       </c>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="F95" s="15" t="inlineStr">
         <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="G72" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="G95" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>檔位 2</t>
         </is>
       </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
         <is>
           <t>12,000,000</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr">
         <is>
           <t>50x</t>
         </is>
       </c>
-      <c r="F73" s="15" t="inlineStr">
+      <c r="F96" s="15" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="G73" s="15" t="inlineStr">
+      <c r="G96" s="15" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="14" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>檔位 3</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
         <is>
           <t>70,000,000</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E97" s="15" t="inlineStr">
         <is>
           <t>20x</t>
         </is>
       </c>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="F97" s="15" t="inlineStr">
         <is>
           <t>2.50%</t>
         </is>
       </c>
-      <c r="G74" s="15" t="inlineStr">
+      <c r="G97" s="15" t="inlineStr">
         <is>
           <t>185,000</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B98" s="14" t="inlineStr">
         <is>
           <t>檔位 4</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>150,000,000</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="E98" s="15" t="inlineStr">
         <is>
           <t>10x</t>
         </is>
       </c>
-      <c r="F75" s="15" t="inlineStr">
+      <c r="F98" s="15" t="inlineStr">
         <is>
           <t>5.00%</t>
         </is>
       </c>
-      <c r="G75" s="15" t="inlineStr">
+      <c r="G98" s="15" t="inlineStr">
         <is>
           <t>1,935,000</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="14" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B99" s="14" t="inlineStr">
         <is>
           <t>檔位 5</t>
         </is>
       </c>
-      <c r="C76" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>300,000,000</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr">
+      <c r="E99" s="15" t="inlineStr">
         <is>
           <t>5x</t>
         </is>
       </c>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="F99" s="15" t="inlineStr">
         <is>
           <t>10.00%</t>
         </is>
       </c>
-      <c r="G76" s="15" t="inlineStr">
+      <c r="G99" s="15" t="inlineStr">
         <is>
           <t>9,435,000</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>檔位 6</t>
         </is>
       </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
         <is>
           <t>400,000,000</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="E100" s="15" t="inlineStr">
         <is>
           <t>2x</t>
         </is>
       </c>
-      <c r="F77" s="15" t="inlineStr">
+      <c r="F100" s="15" t="inlineStr">
         <is>
           <t>25.00%</t>
         </is>
       </c>
-      <c r="G77" s="15" t="inlineStr">
+      <c r="G100" s="15" t="inlineStr">
         <is>
           <t>54,435,000</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>檔位 7</t>
         </is>
       </c>
-      <c r="C78" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>500,000,000</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E101" s="15" t="inlineStr">
         <is>
           <t>1x</t>
         </is>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F101" s="15" t="inlineStr">
         <is>
           <t>50.00%</t>
         </is>
       </c>
-      <c r="G78" s="15" t="inlineStr">
+      <c r="G101" s="15" t="inlineStr">
         <is>
           <t>154,435,000</t>
         </is>

--- a/data/all_exchanges_futures_margin.xlsx
+++ b/data/all_exchanges_futures_margin.xlsx
@@ -547,3156 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="94" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>交易所</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>單位</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>原始資料</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>檔位</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>倉位分級</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>最大槓桿</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>維持保證金率</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>維持金額(USDT)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>內容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>初始保證金 = 倉位價值 / 槓桿</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>維持保證金 = 倉位價值 * 維持保證金比率 - 維持金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>了解更多</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>*最大 倍槓桿 U 本位合約包括：:</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>請注意，在異常價格波動和極端市場行情下，幣安會採取額外的措施來維護市場穩定，包括但不限於：</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>1. 調整最高槓桿倍數</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>2. 調整不同層級的倉位限制</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Binance</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>3. 調整不同層級的維持保證金比率</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>檔位 1</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>320,000</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>150x</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>0.1000%</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>檔位 2</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>1,500,000</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>125x</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>0.2500%</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>檔位 3</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>7,500,000</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>125x</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>0.4000%</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>2,730</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>檔位 4</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>8,500,000</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>62x</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>47,730</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>檔位 5</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>10,000,000</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>62x</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>1.30%</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>73,230</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>檔位 6</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>14,000,000</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>41x</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>93,230</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>檔位 7</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>20,000,000</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>1.60%</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>107,230</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>檔位 8</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>28,000,000</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>187,230</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>檔位 9</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>38,000,000</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>327,230</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>檔位 10</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>50,000,000</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>2.90%</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>479,230</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>檔位 11</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>55,000,000</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>529,230</t>
-        </is>
-      </c>
-      <c r="I20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>檔位 12</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>60,000,000</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>3.50%</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>804,230</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr"/>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>檔位 13</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>65,000,000</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>3.60%</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>864,230</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>檔位 14</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>70,000,000</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>25x</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>3.80%</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>994,230</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr"/>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>檔位 15</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>75,000,000</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>1,134,230</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr"/>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>檔位 16</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>80,000,000</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>4.50%</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>1,509,230</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>檔位 17</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>230,000,000</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>1,909,230</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>檔位 18</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>600,000,000</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>5x</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>12.50%</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>19,159,230</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>檔位 19</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>1,200,000,000</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>3x</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>94,159,230</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr"/>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>檔位 20</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>1,800,000,000</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>394,159,230</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>檔位	價值 (USDT)	槓桿	檔位維持保證金率</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>暫無數據</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>2,000,000</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>2,600,000</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>0.56%</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>1,200</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>3,200,000</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>3,020</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>3,800,000</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>0.67%</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>4,300</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>4,400,000</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>5,820</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr"/>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>5,000,000</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>0.77%</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>8,460</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>5,600,000</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>0.91%</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>15,460</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>8,500,000</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>20,500</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>10,000,000</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>46,000</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>14,000,000</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>66,000</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>20,000,000</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>80,000</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>28,000,000</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>160,000</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>38,000,000</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>50,000,000</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>452,000</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr"/>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>55,000,000</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>502,000</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>60,000,000</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>777,000</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>65,000,000</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>837,000</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>70,000,000</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>967,000</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>75,000,000</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>1,107,000</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>80,000,000</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>1,482,000</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr"/>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>500x</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr"/>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>200x</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="9" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr"/>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="9" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr"/>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>50x</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="9" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr"/>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>1,750</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr"/>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>1,900</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>10x</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr"/>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr"/>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F59" s="11" t="inlineStr">
-        <is>
-          <t>66.66</t>
-        </is>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="H59" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr"/>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>0.75%</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr"/>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>1.25%</t>
-        </is>
-      </c>
-      <c r="H61" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr"/>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>1.75%</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr"/>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>28.57</t>
-        </is>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>2.25%</t>
-        </is>
-      </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr"/>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>2.75%</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr"/>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>1,200</t>
-        </is>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>22.22</t>
-        </is>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>3.25%</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr"/>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>1,400</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>3.75%</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr"/>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>1,600</t>
-        </is>
-      </c>
-      <c r="F67" s="11" t="inlineStr">
-        <is>
-          <t>18.18</t>
-        </is>
-      </c>
-      <c r="G67" s="11" t="inlineStr">
-        <is>
-          <t>4.25%</t>
-        </is>
-      </c>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr"/>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>1,800</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>16.66</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>4.75%</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr"/>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>15.38</t>
-        </is>
-      </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t>5.25%</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr"/>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>2,200</t>
-        </is>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>14.28</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t>5.75%</t>
-        </is>
-      </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr"/>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>13.33</t>
-        </is>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
-        <is>
-          <t>6.25%</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr"/>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="F72" s="11" t="inlineStr">
-        <is>
-          <t>12.50</t>
-        </is>
-      </c>
-      <c r="G72" s="11" t="inlineStr">
-        <is>
-          <t>6.75%</t>
-        </is>
-      </c>
-      <c r="H72" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr"/>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>11.76</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
-        <is>
-          <t>7.25%</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr"/>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="F74" s="11" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="G74" s="11" t="inlineStr">
-        <is>
-          <t>7.75%</t>
-        </is>
-      </c>
-      <c r="H74" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr"/>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="F75" s="11" t="inlineStr">
-        <is>
-          <t>10.52</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr"/>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="F76" s="11" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="inlineStr">
-        <is>
-          <t>8.75%</t>
-        </is>
-      </c>
-      <c r="H76" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr"/>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="F77" s="11" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="G77" s="11" t="inlineStr">
-        <is>
-          <t>9.25%</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="inlineStr"/>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>檔位 1</t>
-        </is>
-      </c>
-      <c r="E78" s="15" t="inlineStr">
-        <is>
-          <t>2,000,000</t>
-        </is>
-      </c>
-      <c r="F78" s="15" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="G78" s="15" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="H78" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" s="15" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr"/>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>檔位 2</t>
-        </is>
-      </c>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>12,000,000</t>
-        </is>
-      </c>
-      <c r="F79" s="15" t="inlineStr">
-        <is>
-          <t>50x</t>
-        </is>
-      </c>
-      <c r="G79" s="15" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="H79" s="15" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="I79" s="15" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="inlineStr"/>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>檔位 3</t>
-        </is>
-      </c>
-      <c r="E80" s="15" t="inlineStr">
-        <is>
-          <t>100,000,000</t>
-        </is>
-      </c>
-      <c r="F80" s="15" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="G80" s="15" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="H80" s="15" t="inlineStr">
-        <is>
-          <t>190,000</t>
-        </is>
-      </c>
-      <c r="I80" s="15" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr"/>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>檔位 4</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>200,000,000</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="inlineStr">
-        <is>
-          <t>10x</t>
-        </is>
-      </c>
-      <c r="G81" s="15" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
-      <c r="H81" s="15" t="inlineStr">
-        <is>
-          <t>2,690,000</t>
-        </is>
-      </c>
-      <c r="I81" s="15" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr"/>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>檔位 5</t>
-        </is>
-      </c>
-      <c r="E82" s="15" t="inlineStr">
-        <is>
-          <t>500,000,000</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr">
-        <is>
-          <t>5x</t>
-        </is>
-      </c>
-      <c r="G82" s="15" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
-      <c r="H82" s="15" t="inlineStr">
-        <is>
-          <t>12,690,000</t>
-        </is>
-      </c>
-      <c r="I82" s="15" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr"/>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>檔位 6</t>
-        </is>
-      </c>
-      <c r="E83" s="15" t="inlineStr">
-        <is>
-          <t>600,000,000</t>
-        </is>
-      </c>
-      <c r="F83" s="15" t="inlineStr">
-        <is>
-          <t>2x</t>
-        </is>
-      </c>
-      <c r="G83" s="15" t="inlineStr">
-        <is>
-          <t>25.00%</t>
-        </is>
-      </c>
-      <c r="H83" s="15" t="inlineStr">
-        <is>
-          <t>87,690,000</t>
-        </is>
-      </c>
-      <c r="I83" s="15" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr"/>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>檔位 7</t>
-        </is>
-      </c>
-      <c r="E84" s="15" t="inlineStr">
-        <is>
-          <t>800,000,000</t>
-        </is>
-      </c>
-      <c r="F84" s="15" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="G84" s="15" t="inlineStr">
-        <is>
-          <t>50.00%</t>
-        </is>
-      </c>
-      <c r="H84" s="15" t="inlineStr">
-        <is>
-          <t>237,690,000</t>
-        </is>
-      </c>
-      <c r="I84" s="15" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3911,7 +762,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>70,000,000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -3948,7 +799,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>65,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3963,7 +814,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>382,000</t>
+          <t>482,000</t>
         </is>
       </c>
     </row>
@@ -3985,7 +836,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>230,000,000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4000,7 +851,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2,007,000</t>
+          <t>2,982,000</t>
         </is>
       </c>
     </row>
@@ -4022,7 +873,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>320,000,000</t>
+          <t>480,000,000</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4037,7 +888,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>9,507,000</t>
+          <t>14,482,000</t>
         </is>
       </c>
     </row>
@@ -4059,7 +910,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>400,000,000</t>
+          <t>600,000,000</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -4074,7 +925,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>17,507,000</t>
+          <t>26,482,000</t>
         </is>
       </c>
     </row>
@@ -4096,7 +947,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>530,000,000</t>
+          <t>800,000,000</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -4111,7 +962,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>27,507,000</t>
+          <t>41,482,000</t>
         </is>
       </c>
     </row>
@@ -4133,7 +984,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>800,000,000</t>
+          <t>1,200,000,000</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -4148,7 +999,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>80,507,000</t>
+          <t>121,482,000</t>
         </is>
       </c>
     </row>
@@ -4170,7 +1021,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1,200,000,000</t>
+          <t>1,800,000,000</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -4185,7 +1036,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>280,507,000</t>
+          <t>421,482,000</t>
         </is>
       </c>
     </row>
@@ -4244,7 +1095,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -4254,12 +1105,12 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>0.3300%</t>
+          <t>0.2500%</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>480</t>
         </is>
       </c>
     </row>
@@ -4281,7 +1132,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>7,500,000</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -4296,7 +1147,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>1,366</t>
+          <t>2,730</t>
         </is>
       </c>
     </row>
@@ -4318,7 +1169,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -4328,12 +1179,12 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>0.7700%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>12,466</t>
+          <t>47,730</t>
         </is>
       </c>
     </row>
@@ -4355,7 +1206,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -4365,12 +1216,12 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>0.9100%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>16,946</t>
+          <t>73,230</t>
         </is>
       </c>
     </row>
@@ -4392,7 +1243,7 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -4402,12 +1253,12 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>20,546</t>
+          <t>93,230</t>
         </is>
       </c>
     </row>
@@ -4429,7 +1280,7 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -4439,12 +1290,12 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>30,546</t>
+          <t>107,230</t>
         </is>
       </c>
     </row>
@@ -4466,7 +1317,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -4476,12 +1327,12 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>38,546</t>
+          <t>187,230</t>
         </is>
       </c>
     </row>
@@ -4503,7 +1354,7 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -4513,12 +1364,12 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>50,546</t>
+          <t>327,230</t>
         </is>
       </c>
     </row>
@@ -4540,7 +1391,7 @@
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>22,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -4550,12 +1401,12 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>66,546</t>
+          <t>479,230</t>
         </is>
       </c>
     </row>
@@ -4577,7 +1428,7 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>55,000,000</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -4587,12 +1438,12 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>176,546</t>
+          <t>529,230</t>
         </is>
       </c>
     </row>
@@ -4614,7 +1465,7 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>32,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -4624,12 +1475,12 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>316,546</t>
+          <t>804,230</t>
         </is>
       </c>
     </row>
@@ -4651,7 +1502,7 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>34,000,000</t>
+          <t>65,000,000</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -4661,12 +1512,12 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>476,546</t>
+          <t>864,230</t>
         </is>
       </c>
     </row>
@@ -4688,7 +1539,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>36,000,000</t>
+          <t>70,000,000</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -4698,12 +1549,12 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>578,546</t>
+          <t>994,230</t>
         </is>
       </c>
     </row>
@@ -4725,22 +1576,22 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>75,000,000</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>650,546</t>
+          <t>1,134,230</t>
         </is>
       </c>
     </row>
@@ -4762,22 +1613,22 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>40,000,000</t>
+          <t>80,000,000</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>764,546</t>
+          <t>1,509,230</t>
         </is>
       </c>
     </row>
@@ -4799,22 +1650,22 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>42,000,000</t>
+          <t>230,000,000</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>804,546</t>
+          <t>1,909,230</t>
         </is>
       </c>
     </row>
@@ -4836,22 +1687,22 @@
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>44,000,000</t>
+          <t>600,000,000</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>930,546</t>
+          <t>19,159,230</t>
         </is>
       </c>
     </row>
@@ -4873,22 +1724,22 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>46,000,000</t>
+          <t>1,200,000,000</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>3x</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>1,062,546</t>
+          <t>94,159,230</t>
         </is>
       </c>
     </row>
@@ -4910,133 +1761,133 @@
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>1,800,000,000</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>1,292,546</t>
+          <t>394,159,230</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>檔位 21</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>400,000,000</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>5x</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>12.50%</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>12,542,546</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>檔位 22</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>800,000,000</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>3x</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>62,542,546</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>檔位 23</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>1,200,000,000</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>262,542,546</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5048,7 +1899,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -5058,17 +1909,17 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -5085,7 +1936,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -5095,17 +1946,17 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -5122,7 +1973,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -5132,17 +1983,17 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -5159,7 +2010,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -5169,17 +2020,17 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>150,000,000</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -5196,27 +2047,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>300,000,000</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>50,000,000</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>12.00%</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -5233,7 +2084,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -5243,17 +2094,17 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>500,000,000</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>15.00%</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -5270,7 +2121,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -5280,17 +2131,17 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>700,000,000</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>20.00%</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -5307,7 +2158,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -5317,17 +2168,17 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>300,000,000</t>
+          <t>900,000,000</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>12.00%</t>
+          <t>30.00%</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -5344,7 +2195,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -5354,17 +2205,17 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>500,000,000</t>
+          <t>1,200,000,000</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>15.00%</t>
+          <t>60.00%</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -5374,113 +2225,113 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>700,000,000</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>2,600,000</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>900,000,000</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>1,200,000,000</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>60.00%</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>3,200,000</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>3,020</t>
         </is>
       </c>
     </row>
@@ -5492,7 +2343,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -5502,22 +2353,22 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,800,000</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4,300</t>
         </is>
       </c>
     </row>
@@ -5529,7 +2380,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -5539,22 +2390,22 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>4,400,000</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>5,820</t>
         </is>
       </c>
     </row>
@@ -5566,7 +2417,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -5576,22 +2427,22 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>3,020</t>
+          <t>8,460</t>
         </is>
       </c>
     </row>
@@ -5603,7 +2454,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -5613,22 +2464,22 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>3,800,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>15,460</t>
         </is>
       </c>
     </row>
@@ -5640,7 +2491,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -5650,22 +2501,22 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>5,820</t>
+          <t>20,500</t>
         </is>
       </c>
     </row>
@@ -5677,7 +2528,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -5687,22 +2538,22 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>8,460</t>
+          <t>46,000</t>
         </is>
       </c>
     </row>
@@ -5714,7 +2565,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -5724,22 +2575,22 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>15,460</t>
+          <t>66,000</t>
         </is>
       </c>
     </row>
@@ -5751,7 +2602,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -5761,22 +2612,22 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>80,000</t>
         </is>
       </c>
     </row>
@@ -5788,7 +2639,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -5798,22 +2649,22 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>160,000</t>
         </is>
       </c>
     </row>
@@ -5825,7 +2676,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -5835,22 +2686,22 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>14,000,000</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>300,000</t>
         </is>
       </c>
     </row>
@@ -5862,7 +2713,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -5872,22 +2723,22 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>20,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>452,000</t>
         </is>
       </c>
     </row>
@@ -5899,7 +2750,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -5909,22 +2760,22 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>55,000,000</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>502,000</t>
         </is>
       </c>
     </row>
@@ -5936,7 +2787,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -5946,22 +2797,22 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>777,000</t>
         </is>
       </c>
     </row>
@@ -5973,7 +2824,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -5983,22 +2834,22 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>65,000,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>452,000</t>
+          <t>837,000</t>
         </is>
       </c>
     </row>
@@ -6010,7 +2861,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -6020,22 +2871,22 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>55,000,000</t>
+          <t>70,000,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>502,000</t>
+          <t>967,000</t>
         </is>
       </c>
     </row>
@@ -6047,7 +2898,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -6057,22 +2908,22 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>75,000,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>777,000</t>
+          <t>1,107,000</t>
         </is>
       </c>
     </row>
@@ -6084,7 +2935,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -6094,133 +2945,133 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>65,000,000</t>
+          <t>80,000,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>837,000</t>
+          <t>1,482,000</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>70,000,000</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>967,000</t>
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>500x</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>75,000,000</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>1,107,000</t>
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>200x</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>80,000,000</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>1,482,000</t>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6232,27 +3083,27 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>500x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -6269,27 +3120,27 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>1,070</t>
+          <t>1,750</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>200x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -6306,141 +3157,141 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>66.66</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>8,600</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>50x</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>45,000</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>20x</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>48,000</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>10x</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6454,27 +3305,27 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6491,27 +3342,27 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>66.66</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
@@ -6528,27 +3379,27 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>800</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6565,27 +3416,27 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -6602,27 +3453,27 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6639,27 +3490,27 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>1,400</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -6676,27 +3527,27 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>1,600</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6713,27 +3564,27 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -6750,27 +3601,27 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>17,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>5.25%</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6787,27 +3638,27 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>2,200</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -6824,27 +3675,27 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>22,500</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6861,27 +3712,27 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>6.75%</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
@@ -6898,27 +3749,27 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>27,500</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>7.25%</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6935,27 +3786,27 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>7.75%</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
@@ -6972,27 +3823,27 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>32,500</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>6.75%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7009,27 +3860,27 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>8.75%</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -7046,27 +3897,27 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>37,500</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>7.75%</t>
+          <t>9.25%</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7076,113 +3927,113 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C92" s="10" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="D92" s="11" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>10.52</t>
-        </is>
-      </c>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="inlineStr">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>檔位 1</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>42,500</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>8.75%</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>檔位 2</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>12,000,000</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>10,000</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr">
-        <is>
-          <t>45,000</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>9.25%</t>
-        </is>
-      </c>
-      <c r="G94" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>檔位 3</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>190,000</t>
         </is>
       </c>
     </row>
@@ -7194,7 +4045,7 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>檔位 1</t>
+          <t>檔位 4</t>
         </is>
       </c>
       <c r="C95" s="14" t="inlineStr">
@@ -7204,22 +4055,22 @@
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G95" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2,690,000</t>
         </is>
       </c>
     </row>
@@ -7231,7 +4082,7 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>檔位 2</t>
+          <t>檔位 5</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
@@ -7241,22 +4092,22 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>500,000,000</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>50x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>12,690,000</t>
         </is>
       </c>
     </row>
@@ -7268,7 +4119,7 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>檔位 3</t>
+          <t>檔位 6</t>
         </is>
       </c>
       <c r="C97" s="14" t="inlineStr">
@@ -7278,22 +4129,22 @@
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>70,000,000</t>
+          <t>600,000,000</t>
         </is>
       </c>
       <c r="E97" s="15" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>25.00%</t>
         </is>
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>185,000</t>
+          <t>87,690,000</t>
         </is>
       </c>
     </row>
@@ -7305,141 +4156,2939 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
+          <t>檔位 7</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>800,000,000</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>237,690,000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>交易所</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>檔位</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>倉位分級</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>最大槓桿</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>維持保證金率</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>維持金額(USDT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>150x</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>800,000</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>3,000,000</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>75x</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>12,000,000</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>25x</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>132,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>65,000,000</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>382,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>150,000,000</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2,007,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>320,000,000</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>5x</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>9,507,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>400,000,000</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>12.50%</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>17,507,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>530,000,000</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>15.00%</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>27,507,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>800,000,000</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>80,507,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>1,200,000,000</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>280,507,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>15,000,000</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2.00%</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>100,000,000</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>150,000,000</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>300,000,000</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>12.00%</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>500,000,000</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>15.00%</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>700,000,000</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>900,000,000</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>1,200,000,000</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>60.00%</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2,600,000</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>3,200,000</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>3,020</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>3,800,000</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0.67%</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>4,400,000</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>5,820</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>8,460</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>5,600,000</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>15,460</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>8,500,000</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>20,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>46,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>14,000,000</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>66,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>20,000,000</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>28,000,000</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>160,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>38,000,000</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>300,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>452,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>55,000,000</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>502,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>60,000,000</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>777,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>65,000,000</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>837,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>70,000,000</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>967,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>75,000,000</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>1,107,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>80,000,000</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>1,482,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>500x</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>1,070</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>200x</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>48,000</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>66.66</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>28.57</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>2.25%</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>2.75%</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>22.22</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>17,500</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>3.75%</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>4.25%</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>22,500</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>16.66</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>15.38</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>27,500</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>14.28</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>5.75%</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>30,000</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>6.25%</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>32,500</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>12.50</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>6.75%</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>35,000</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>11.76</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>7.25%</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>37,500</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>7.75%</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>10.52</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>42,500</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t>8.75%</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>45,000</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>9.52</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>9.25%</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>檔位 1</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>1,000,000</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>檔位 2</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>12,000,000</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>50x</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>檔位 3</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>70,000,000</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>185,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
           <t>檔位 4</t>
         </is>
       </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
         <is>
           <t>150,000,000</t>
         </is>
       </c>
-      <c r="E98" s="15" t="inlineStr">
+      <c r="E75" s="15" t="inlineStr">
         <is>
           <t>10x</t>
         </is>
       </c>
-      <c r="F98" s="15" t="inlineStr">
+      <c r="F75" s="15" t="inlineStr">
         <is>
           <t>5.00%</t>
         </is>
       </c>
-      <c r="G98" s="15" t="inlineStr">
+      <c r="G75" s="15" t="inlineStr">
         <is>
           <t>1,935,000</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B99" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>檔位 5</t>
         </is>
       </c>
-      <c r="C99" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D99" s="15" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
         <is>
           <t>300,000,000</t>
         </is>
       </c>
-      <c r="E99" s="15" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr">
         <is>
           <t>5x</t>
         </is>
       </c>
-      <c r="F99" s="15" t="inlineStr">
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>10.00%</t>
         </is>
       </c>
-      <c r="G99" s="15" t="inlineStr">
+      <c r="G76" s="15" t="inlineStr">
         <is>
           <t>9,435,000</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="14" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B100" s="14" t="inlineStr">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>檔位 6</t>
         </is>
       </c>
-      <c r="C100" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D100" s="15" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>400,000,000</t>
         </is>
       </c>
-      <c r="E100" s="15" t="inlineStr">
+      <c r="E77" s="15" t="inlineStr">
         <is>
           <t>2x</t>
         </is>
       </c>
-      <c r="F100" s="15" t="inlineStr">
+      <c r="F77" s="15" t="inlineStr">
         <is>
           <t>25.00%</t>
         </is>
       </c>
-      <c r="G100" s="15" t="inlineStr">
+      <c r="G77" s="15" t="inlineStr">
         <is>
           <t>54,435,000</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>檔位 7</t>
         </is>
       </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
         <is>
           <t>500,000,000</t>
         </is>
       </c>
-      <c r="E101" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr">
         <is>
           <t>1x</t>
         </is>
       </c>
-      <c r="F101" s="15" t="inlineStr">
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>50.00%</t>
         </is>
       </c>
-      <c r="G101" s="15" t="inlineStr">
+      <c r="G78" s="15" t="inlineStr">
         <is>
           <t>154,435,000</t>
         </is>

--- a/data/all_exchanges_futures_margin.xlsx
+++ b/data/all_exchanges_futures_margin.xlsx
@@ -2242,17 +2242,17 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2279,22 +2279,22 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>510</t>
         </is>
       </c>
     </row>
@@ -2316,22 +2316,22 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>3,020</t>
+          <t>1,710</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2353,22 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>3,800,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,530</t>
         </is>
       </c>
     </row>
@@ -2390,22 +2390,22 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>3,800,000</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>5,820</t>
+          <t>4,810</t>
         </is>
       </c>
     </row>
@@ -2427,22 +2427,22 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,400,000</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>8,460</t>
+          <t>6,330</t>
         </is>
       </c>
     </row>
@@ -2464,22 +2464,22 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>15,460</t>
+          <t>8,970</t>
         </is>
       </c>
     </row>
@@ -2501,22 +2501,22 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>15,970</t>
         </is>
       </c>
     </row>
@@ -2538,22 +2538,22 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>46,000</t>
+          <t>21,010</t>
         </is>
       </c>
     </row>
@@ -2575,22 +2575,22 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>14,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>66,000</t>
+          <t>46,510</t>
         </is>
       </c>
     </row>
@@ -2612,22 +2612,22 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>20,000,000</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>66,510</t>
         </is>
       </c>
     </row>
@@ -2649,22 +2649,22 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>80,510</t>
         </is>
       </c>
     </row>
@@ -2686,22 +2686,22 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>160,510</t>
         </is>
       </c>
     </row>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>452,000</t>
+          <t>300,510</t>
         </is>
       </c>
     </row>
@@ -2760,22 +2760,22 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>55,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>502,000</t>
+          <t>452,510</t>
         </is>
       </c>
     </row>
@@ -2797,22 +2797,22 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>55,000,000</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>777,000</t>
+          <t>502,510</t>
         </is>
       </c>
     </row>
@@ -2834,22 +2834,22 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>65,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>837,000</t>
+          <t>777,510</t>
         </is>
       </c>
     </row>
@@ -2871,22 +2871,22 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>70,000,000</t>
+          <t>65,000,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>967,000</t>
+          <t>837,510</t>
         </is>
       </c>
     </row>
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>75,000,000</t>
+          <t>70,000,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>1,107,000</t>
+          <t>967,510</t>
         </is>
       </c>
     </row>
@@ -2945,22 +2945,22 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>80,000,000</t>
+          <t>75,000,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>1,482,000</t>
+          <t>1,107,510</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>62x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>62x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>41x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>7x</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -6113,17 +6113,17 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -6150,22 +6150,22 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>510</t>
         </is>
       </c>
     </row>
@@ -6187,22 +6187,22 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>1,380</t>
+          <t>1,050</t>
         </is>
       </c>
     </row>
@@ -6224,22 +6224,22 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>1,980</t>
+          <t>1,890</t>
         </is>
       </c>
     </row>
@@ -6261,22 +6261,22 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>1,800,000</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>2,700</t>
+          <t>2,490</t>
         </is>
       </c>
     </row>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>4,140</t>
+          <t>3,210</t>
         </is>
       </c>
     </row>
@@ -6335,22 +6335,22 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>8,620</t>
+          <t>4,650</t>
         </is>
       </c>
     </row>
@@ -6372,22 +6372,22 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>12,220</t>
+          <t>9,130</t>
         </is>
       </c>
     </row>
@@ -6409,22 +6409,22 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>22,220</t>
+          <t>12,730</t>
         </is>
       </c>
     </row>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>30,220</t>
+          <t>22,730</t>
         </is>
       </c>
     </row>
@@ -6483,22 +6483,22 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>42,220</t>
+          <t>30,730</t>
         </is>
       </c>
     </row>
@@ -6520,22 +6520,22 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>22,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>58,220</t>
+          <t>42,730</t>
         </is>
       </c>
     </row>
@@ -6557,22 +6557,22 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>22,000,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>168,220</t>
+          <t>58,730</t>
         </is>
       </c>
     </row>
@@ -6594,22 +6594,22 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>32,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>308,220</t>
+          <t>168,730</t>
         </is>
       </c>
     </row>
@@ -6631,22 +6631,22 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>34,000,000</t>
+          <t>32,000,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>468,220</t>
+          <t>308,730</t>
         </is>
       </c>
     </row>
@@ -6668,22 +6668,22 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>36,000,000</t>
+          <t>34,000,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>570,220</t>
+          <t>468,730</t>
         </is>
       </c>
     </row>
@@ -6705,22 +6705,22 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>38,000,000</t>
+          <t>36,000,000</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>642,220</t>
+          <t>570,730</t>
         </is>
       </c>
     </row>
@@ -6742,22 +6742,22 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>40,000,000</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>756,220</t>
+          <t>642,730</t>
         </is>
       </c>
     </row>
@@ -6779,22 +6779,22 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>42,000,000</t>
+          <t>40,000,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>796,220</t>
+          <t>756,730</t>
         </is>
       </c>
     </row>
@@ -6816,22 +6816,22 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>44,000,000</t>
+          <t>42,000,000</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>922,220</t>
+          <t>796,730</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>13,000,000</t>
+          <t>17,000,000</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>30,000,000</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>227,676</t>
+          <t>637,676</t>
         </is>
       </c>
     </row>
@@ -8615,22 +8615,22 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>30,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>527,676</t>
+          <t>1,837,676</t>
         </is>
       </c>
     </row>
@@ -8652,22 +8652,22 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>80,000,000</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>1,727,676</t>
+          <t>3,037,676</t>
         </is>
       </c>
     </row>
@@ -8689,22 +8689,22 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>80,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>13.33%</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>2,927,676</t>
+          <t>5,701,676</t>
         </is>
       </c>
     </row>
@@ -8726,22 +8726,22 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>150,000,000</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>4x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>13.33%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>5,591,676</t>
+          <t>12,371,676</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>300,000,000</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>12,261,676</t>
+          <t>42,371,676</t>
         </is>
       </c>
     </row>
@@ -8800,59 +8800,59 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>300,000,000</t>
+          <t>400,000,000</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>2x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>42,261,676</t>
+          <t>72,371,676</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>檔位 10</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>400,000,000</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>72,261,676</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -8874,17 +8874,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -8948,17 +8948,17 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -8985,17 +8985,17 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -9022,17 +9022,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>30,000,000</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>30,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>12.00%</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -9096,17 +9096,17 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>80,000,000</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>12.00%</t>
+          <t>15.00%</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -9133,17 +9133,17 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>80,000,000</t>
+          <t>150,000,000</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>15.00%</t>
+          <t>30.00%</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -9170,17 +9170,17 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>150,000,000</t>
+          <t>300,000,000</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>30.00%</t>
+          <t>60.00%</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -9190,39 +9190,39 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>300,000,000</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>60.00%</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -9244,22 +9244,22 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -9281,22 +9281,22 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -9318,22 +9318,22 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -9355,22 +9355,22 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>550,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>360</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -9392,22 +9392,22 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>550,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>690</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -9429,22 +9429,22 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>850,000</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>1,670</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -9466,22 +9466,22 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>850,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>1,670</t>
+          <t>2,435</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -9503,22 +9503,22 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>2,435</t>
+          <t>3,535</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -9540,22 +9540,22 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>3,535</t>
+          <t>6,335</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -9577,22 +9577,22 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>6,335</t>
+          <t>11,735</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>11,735</t>
+          <t>21,335</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -9651,22 +9651,22 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>21,335</t>
+          <t>41,135</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -9688,22 +9688,22 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>41,135</t>
+          <t>81,135</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -9725,22 +9725,22 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.63%</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>81,135</t>
+          <t>94,135</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -9762,22 +9762,22 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>94,135</t>
+          <t>112,135</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -9799,22 +9799,22 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>14,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>112,135</t>
+          <t>134,535</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -9836,22 +9836,22 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>134,535</t>
+          <t>164,935</t>
         </is>
       </c>
     </row>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -9873,22 +9873,22 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>18,000,000</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>164,935</t>
+          <t>200,935</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -9910,59 +9910,59 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>20,000,000</t>
+          <t>22,000,000</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>200,935</t>
+          <t>248,935</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>22,000,000</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>3.57%</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>248,935</t>
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>300x</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9974,67 +9974,67 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>118,500</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>200x</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>SOL</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>300x</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>SOL</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>160,000</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>200x</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -10058,17 +10058,17 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>66.66</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -10095,17 +10095,17 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>66.66</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -10132,17 +10132,17 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -10169,17 +10169,17 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -10206,17 +10206,17 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>80,000</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -10243,17 +10243,17 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>80,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -10280,17 +10280,17 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>120,000</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -10317,17 +10317,17 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>120,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -10354,17 +10354,17 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -10391,17 +10391,17 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>5.25%</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -10465,17 +10465,17 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>220,000</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -10502,17 +10502,17 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>220,000</t>
+          <t>240,000</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -10539,17 +10539,17 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>260,000</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.75%</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>260,000</t>
+          <t>280,000</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>6.75%</t>
+          <t>7.25%</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -10613,17 +10613,17 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>280,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>7.75%</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -10650,17 +10650,17 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>320,000</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>7.75%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -10687,17 +10687,17 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>320,000</t>
+          <t>340,000</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>8.25%</t>
+          <t>8.75%</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -10724,17 +10724,17 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>340,000</t>
+          <t>360,000</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>9.25%</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
@@ -10744,37 +10744,37 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>SOL</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>360,000</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>9.25%</t>
-        </is>
-      </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>檔位 1</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>100x</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>檔位 1</t>
+          <t>檔位 2</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -10798,22 +10798,22 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>75x</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>檔位 2</t>
+          <t>檔位 3</t>
         </is>
       </c>
       <c r="C75" s="14" t="inlineStr">
@@ -10835,22 +10835,22 @@
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>75x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G75" s="15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1,475</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>檔位 3</t>
+          <t>檔位 4</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -10872,22 +10872,22 @@
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>50x</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
         <is>
-          <t>1,475</t>
+          <t>11,475</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>檔位 4</t>
+          <t>檔位 5</t>
         </is>
       </c>
       <c r="C77" s="14" t="inlineStr">
@@ -10909,22 +10909,22 @@
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>40,000,000</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr">
         <is>
-          <t>11,475</t>
+          <t>131,475</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>檔位 5</t>
+          <t>檔位 6</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -10946,22 +10946,22 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>40,000,000</t>
+          <t>80,000,000</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
         <is>
-          <t>131,475</t>
+          <t>2,131,475</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>檔位 6</t>
+          <t>檔位 7</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
@@ -10983,22 +10983,22 @@
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>80,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>25.00%</t>
         </is>
       </c>
       <c r="G79" s="15" t="inlineStr">
         <is>
-          <t>2,131,475</t>
+          <t>14,131,475</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>檔位 7</t>
+          <t>檔位 8</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -11020,57 +11020,20 @@
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>400,000,000</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>2x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>25.00%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
-        <is>
-          <t>14,131,475</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>檔位 8</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>400,000,000</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="inlineStr">
-        <is>
-          <t>50.00%</t>
-        </is>
-      </c>
-      <c r="G81" s="15" t="inlineStr">
         <is>
           <t>64,131,475</t>
         </is>
@@ -14107,7 +14070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -14581,7 +14544,7 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>2,900,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -14618,7 +14581,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -14628,12 +14591,12 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>65,317.2</t>
+          <t>166,317.2</t>
         </is>
       </c>
     </row>
@@ -14655,22 +14618,22 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>13.30%</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>140,317.2</t>
+          <t>1,411,317.2</t>
         </is>
       </c>
     </row>
@@ -14692,22 +14655,22 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>20,000,000</t>
+          <t>30,000,000</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>13.30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>1,385,317.2</t>
+          <t>2,751,317.2</t>
         </is>
       </c>
     </row>
@@ -14729,22 +14692,22 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>30,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>2,725,317.2</t>
+          <t>8,751,317.2</t>
         </is>
       </c>
     </row>
@@ -14766,59 +14729,59 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>3x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>8,725,317.2</t>
+          <t>13,751,317.2</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>檔位 8</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>100,000,000</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>13,725,317.2</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14793,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -14840,17 +14803,17 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -14867,7 +14830,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -14877,17 +14840,17 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -14904,7 +14867,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -14914,17 +14877,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -14941,7 +14904,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -14951,17 +14914,17 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,300,000</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -14978,7 +14941,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -14988,17 +14951,17 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>1,300,000</t>
+          <t>3,300,000</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -15015,7 +14978,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -15025,17 +14988,17 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>3,300,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>12.00%</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -15052,7 +15015,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15062,17 +15025,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>25,000,000</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>12.00%</t>
+          <t>15.00%</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -15089,7 +15052,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15099,17 +15062,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>25,000,000</t>
+          <t>31,000,000</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>15.00%</t>
+          <t>30.00%</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -15126,7 +15089,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15136,17 +15099,17 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>31,000,000</t>
+          <t>35,000,000</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>30.00%</t>
+          <t>60.00%</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -15156,39 +15119,39 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>35,000,000</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>60.00%</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15163,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -15210,22 +15173,22 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15200,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -15247,22 +15210,22 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2,000</t>
         </is>
       </c>
     </row>
@@ -15274,7 +15237,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -15284,22 +15247,22 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>4,500</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15274,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -15321,22 +15284,22 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,300,000</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>9,000</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15311,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -15358,22 +15321,22 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>1,300,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>15,500</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15348,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -15395,22 +15358,22 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>2,100,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>15,500</t>
+          <t>24,000</t>
         </is>
       </c>
     </row>
@@ -15422,7 +15385,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -15432,22 +15395,22 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>2,100,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>24,000</t>
+          <t>34,500</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15422,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -15469,22 +15432,22 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>2,900,000</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>34,500</t>
+          <t>47,000</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15459,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -15506,22 +15469,22 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>2,900,000</t>
+          <t>3,300,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>47,000</t>
+          <t>61,500</t>
         </is>
       </c>
     </row>
@@ -15533,7 +15496,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -15543,22 +15506,22 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>3,300,000</t>
+          <t>3,700,000</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>61,500</t>
+          <t>78,000</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15533,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -15580,22 +15543,22 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>3,700,000</t>
+          <t>4,100,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>78,000</t>
+          <t>96,500</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15570,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -15617,22 +15580,22 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>4,100,000</t>
+          <t>4,500,000</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>96,500</t>
+          <t>117,000</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15607,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -15654,22 +15617,22 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>4,900,000</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>117,000</t>
+          <t>139,500</t>
         </is>
       </c>
     </row>
@@ -15681,7 +15644,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -15691,22 +15654,22 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>4,900,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>139,500</t>
+          <t>164,000</t>
         </is>
       </c>
     </row>
@@ -15718,7 +15681,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -15728,22 +15691,22 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>189,000</t>
         </is>
       </c>
     </row>
@@ -15755,7 +15718,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -15765,22 +15728,22 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>189,000</t>
+          <t>224,000</t>
         </is>
       </c>
     </row>
@@ -15792,7 +15755,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -15802,22 +15765,22 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>224,000</t>
+          <t>269,000</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15792,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -15839,22 +15802,22 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>13,000,000</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>269,000</t>
+          <t>324,000</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15829,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -15876,59 +15839,59 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>13,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>324,000</t>
+          <t>389,000</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>15,000,000</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>389,000</t>
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>550,000</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>300x</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15940,67 +15903,67 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>10,500,000</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>200x</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>ADA</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>550,000</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>300x</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>ADA</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>13,500,000</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>200x</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>220,000</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16014,7 +15977,7 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -16024,17 +15987,17 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>220,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -16051,7 +16014,7 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -16061,17 +16024,17 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -16088,7 +16051,7 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -16098,17 +16061,17 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -16125,7 +16088,7 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -16135,17 +16098,17 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -16162,7 +16125,7 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -16172,17 +16135,17 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -16199,7 +16162,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -16209,17 +16172,17 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -16236,7 +16199,7 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -16246,17 +16209,17 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -16273,7 +16236,7 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -16283,17 +16246,17 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -16310,7 +16273,7 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -16320,17 +16283,17 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>6.50%</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -16347,7 +16310,7 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -16357,17 +16320,17 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>6.50%</t>
+          <t>7.00%</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -16384,7 +16347,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -16394,17 +16357,17 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>7.00%</t>
+          <t>7.50%</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -16421,7 +16384,7 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -16431,17 +16394,17 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>7.50%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -16458,7 +16421,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -16468,17 +16431,17 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
@@ -16495,7 +16458,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -16505,17 +16468,17 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>13,000,000</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -16532,7 +16495,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -16542,17 +16505,17 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>13,000,000</t>
+          <t>14,000,000</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9.50%</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -16569,7 +16532,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -16579,17 +16542,17 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>14,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>9.50%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -16606,7 +16569,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -16616,17 +16579,17 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>15,000,000</t>
+          <t>16,000,000</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>10.50%</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
@@ -16643,7 +16606,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -16653,17 +16616,17 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>16,000,000</t>
+          <t>17,000,000</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>10.50%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -16680,7 +16643,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -16690,17 +16653,17 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>17,000,000</t>
+          <t>18,000,000</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>11.50%</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -16710,37 +16673,37 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>ADA</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>18,000,000</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>7.40</t>
-        </is>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>11.50%</t>
-        </is>
-      </c>
-      <c r="G71" s="11" t="inlineStr">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>檔位 1</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>75x</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16754,7 +16717,7 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>檔位 1</t>
+          <t>檔位 2</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -16764,22 +16727,22 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>75x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -16791,7 +16754,7 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>檔位 2</t>
+          <t>檔位 3</t>
         </is>
       </c>
       <c r="C73" s="14" t="inlineStr">
@@ -16801,22 +16764,22 @@
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>50x</t>
+          <t>40x</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="G73" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16791,7 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>檔位 3</t>
+          <t>檔位 4</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -16838,22 +16801,22 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>40x</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,300</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16828,7 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>檔位 4</t>
+          <t>檔位 5</t>
         </is>
       </c>
       <c r="C75" s="14" t="inlineStr">
@@ -16875,22 +16838,22 @@
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="G75" s="15" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>6,300</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16865,7 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>檔位 5</t>
+          <t>檔位 6</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -16912,22 +16875,22 @@
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
         <is>
-          <t>6,300</t>
+          <t>56,300</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16902,7 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>檔位 6</t>
+          <t>檔位 7</t>
         </is>
       </c>
       <c r="C77" s="14" t="inlineStr">
@@ -16949,22 +16912,22 @@
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>20,000,000</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr">
         <is>
-          <t>56,300</t>
+          <t>556,300</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16939,7 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>檔位 7</t>
+          <t>檔位 8</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -16986,22 +16949,22 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>20,000,000</t>
+          <t>25,000,000</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
         <is>
-          <t>556,300</t>
+          <t>1,056,300</t>
         </is>
       </c>
     </row>
@@ -17013,7 +16976,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>檔位 8</t>
+          <t>檔位 9</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
@@ -17023,22 +16986,22 @@
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>25,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>4x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>12.50%</t>
+          <t>25.00%</t>
         </is>
       </c>
       <c r="G79" s="15" t="inlineStr">
         <is>
-          <t>1,056,300</t>
+          <t>4,181,300</t>
         </is>
       </c>
     </row>
@@ -17050,7 +17013,7 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>檔位 9</t>
+          <t>檔位 10</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -17060,57 +17023,20 @@
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>2x</t>
+          <t>1x</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>25.00%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
-        <is>
-          <t>4,181,300</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>Pionex (派網)</t>
-        </is>
-      </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>檔位 10</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>100,000,000</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>1x</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="inlineStr">
-        <is>
-          <t>50.00%</t>
-        </is>
-      </c>
-      <c r="G81" s="15" t="inlineStr">
         <is>
           <t>16,681,300</t>
         </is>
@@ -17569,7 +17495,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -17606,7 +17532,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -17643,7 +17569,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -17680,7 +17606,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -17717,7 +17643,7 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -17754,7 +17680,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -17791,7 +17717,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -17828,7 +17754,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -18970,7 +18896,7 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>26,970</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -20584,12 +20510,12 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>2,700,000</t>
+          <t>3,400,000</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>200x</t>
+          <t>300x</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -20621,7 +20547,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -20636,7 +20562,7 @@
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>47,394</t>
+          <t>59,644</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20589,7 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>25x</t>
+          <t>15x</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -20673,7 +20599,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>612,794</t>
+          <t>830,644</t>
         </is>
       </c>
     </row>
@@ -20710,7 +20636,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>1,899,794</t>
+          <t>2,117,644</t>
         </is>
       </c>
     </row>
@@ -20747,7 +20673,7 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>3,399,794</t>
+          <t>3,617,644</t>
         </is>
       </c>
     </row>
@@ -20784,7 +20710,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>6,735,794</t>
+          <t>6,953,644</t>
         </is>
       </c>
     </row>
@@ -20821,7 +20747,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>15,065,794</t>
+          <t>15,283,644</t>
         </is>
       </c>
     </row>
@@ -20858,7 +20784,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>77,565,794</t>
+          <t>77,783,644</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22064,7 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>10,800,000</t>
+          <t>8,535,000</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -23315,7 +23241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -23382,17 +23308,17 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -23419,22 +23345,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>150,000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -23456,22 +23382,22 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>9,180</t>
+          <t>1,250</t>
         </is>
       </c>
     </row>
@@ -23493,22 +23419,22 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>750,000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>5x</t>
+          <t>15x</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>109,180</t>
+          <t>3,740</t>
         </is>
       </c>
     </row>
@@ -23530,22 +23456,22 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>12.50%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>234,180</t>
+          <t>16,265</t>
         </is>
       </c>
     </row>
@@ -23567,22 +23493,22 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>25,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>3x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>651,180</t>
+          <t>166,265</t>
         </is>
       </c>
     </row>
@@ -23604,22 +23530,22 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>25.00%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2,733,680</t>
+          <t>416,265</t>
         </is>
       </c>
     </row>
@@ -23641,96 +23567,96 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t>25,000,000</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>3x</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>1,041,765</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>3,124,265</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
           <t>100,000,000</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>1x</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>50.00%</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>15,233,680</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>檔位 1</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>51,000</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>0.5000%</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>BingX</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>檔位 2</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>65,000</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>255</t>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>15,624,265</t>
         </is>
       </c>
     </row>
@@ -23742,7 +23668,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>檔位 3</t>
+          <t>檔位 1</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -23752,22 +23678,22 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>50x</t>
+          <t>100x</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>0.5000%</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>1,769.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23705,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>檔位 4</t>
+          <t>檔位 2</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -23789,22 +23715,22 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>100x</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>10,119.5</t>
+          <t>255</t>
         </is>
       </c>
     </row>
@@ -23816,7 +23742,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>檔位 5</t>
+          <t>檔位 3</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -23826,22 +23752,22 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>110,119.5</t>
+          <t>2,398.6</t>
         </is>
       </c>
     </row>
@@ -23853,7 +23779,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>檔位 6</t>
+          <t>檔位 4</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -23863,22 +23789,22 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>4x</t>
+          <t>15x</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>12.50%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>235,119.5</t>
+          <t>10,748.6</t>
         </is>
       </c>
     </row>
@@ -23890,7 +23816,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>檔位 7</t>
+          <t>檔位 5</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -23900,22 +23826,22 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>25,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>3x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>652,119.5</t>
+          <t>110,748.6</t>
         </is>
       </c>
     </row>
@@ -23927,7 +23853,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>檔位 8</t>
+          <t>檔位 6</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -23937,22 +23863,22 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>1x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.50%</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>2,734,619.5</t>
+          <t>235,748.6</t>
         </is>
       </c>
     </row>
@@ -23964,106 +23890,106 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
+          <t>檔位 7</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>25,000,000</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>16.67%</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>652,748.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>檔位 8</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>2,735,248.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>BingX</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
           <t>檔位 9</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>100,000,000</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>100x</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>15,234,619.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>2.00%</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Bitget</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>500,000</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>3.00%</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>15,235,248.6</t>
         </is>
       </c>
     </row>
@@ -24075,7 +24001,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -24085,17 +24011,17 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -24112,7 +24038,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -24122,17 +24048,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -24149,7 +24075,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -24159,17 +24085,17 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>7.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -24186,7 +24112,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -24196,17 +24122,17 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>12.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -24223,7 +24149,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -24238,12 +24164,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>15.00%</t>
+          <t>12.00%</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -24260,7 +24186,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -24270,17 +24196,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>25,000,000</t>
+          <t>15,000,000</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>20.00%</t>
+          <t>15.00%</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -24297,7 +24223,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -24307,17 +24233,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>25,000,000</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>30.00%</t>
+          <t>20.00%</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -24334,7 +24260,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -24344,59 +24270,59 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>50,000,000</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
           <t>100,000,000</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>60.00%</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Bybit</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24334,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -24418,22 +24344,22 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -24445,7 +24371,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -24455,22 +24381,22 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -24482,7 +24408,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -24492,22 +24418,22 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>88</t>
         </is>
       </c>
     </row>
@@ -24519,7 +24445,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -24529,22 +24455,22 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>140.8</t>
         </is>
       </c>
     </row>
@@ -24556,7 +24482,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -24566,22 +24492,22 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>285.6</t>
+          <t>224.8</t>
         </is>
       </c>
     </row>
@@ -24593,7 +24519,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -24603,22 +24529,22 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>366.6</t>
+          <t>285.6</t>
         </is>
       </c>
     </row>
@@ -24630,7 +24556,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -24640,22 +24566,22 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>23,500</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>478.6</t>
+          <t>366.6</t>
         </is>
       </c>
     </row>
@@ -24667,32 +24593,32 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>23,500</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>27,000</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>640.75</t>
+          <t>478.6</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24630,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -24714,22 +24640,22 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>30,500</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>6.67%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>754.15</t>
+          <t>640.75</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24667,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -24751,22 +24677,22 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>30,500</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>7.14%</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>897.5</t>
+          <t>754.15</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24704,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -24788,22 +24714,22 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>37,500</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>7.14%</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>1,084.5</t>
+          <t>897.5</t>
         </is>
       </c>
     </row>
@@ -24815,7 +24741,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -24825,22 +24751,22 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>37,500</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>1,324.5</t>
+          <t>1,084.5</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24778,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -24862,22 +24788,22 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>44,500</t>
+          <t>41,000</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>1,636.1</t>
+          <t>1,324.5</t>
         </is>
       </c>
     </row>
@@ -24889,7 +24815,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -24899,22 +24825,22 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>44,500</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>2,041.05</t>
+          <t>1,636.1</t>
         </is>
       </c>
     </row>
@@ -24926,7 +24852,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -24936,22 +24862,22 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>62,500</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>10.53%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>2,306.05</t>
+          <t>2,041.05</t>
         </is>
       </c>
     </row>
@@ -24963,7 +24889,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -24973,22 +24899,22 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>62,500</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>11.11%</t>
+          <t>10.53%</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>2,668.55</t>
+          <t>2,306.05</t>
         </is>
       </c>
     </row>
@@ -25000,7 +24926,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -25010,22 +24936,22 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>87,500</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>11.76%</t>
+          <t>11.11%</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>3,156.05</t>
+          <t>2,668.55</t>
         </is>
       </c>
     </row>
@@ -25037,7 +24963,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -25047,22 +24973,22 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>87,500</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.76%</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>3,803.55</t>
+          <t>3,156.05</t>
         </is>
       </c>
     </row>
@@ -25074,69 +25000,69 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>3,803.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>125,000</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>13.33%</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>4,633.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>MEXC</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>500x</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -25148,7 +25074,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -25158,17 +25084,17 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>200x</t>
+          <t>500x</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -25185,7 +25111,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -25195,17 +25121,17 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>200x</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -25222,7 +25148,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -25232,17 +25158,17 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>50x</t>
+          <t>100x</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -25259,7 +25185,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -25269,17 +25195,17 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>1,750</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>50x</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -25296,67 +25222,67 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>1,750</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>20x</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>MEXC</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>MSTR</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>1,900</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>10x</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>OKX</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>2.00%</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -25370,7 +25296,7 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -25380,17 +25306,17 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>1,200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -25407,7 +25333,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -25417,17 +25343,17 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>1,200</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -25444,7 +25370,7 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -25454,17 +25380,17 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -25481,7 +25407,7 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -25491,17 +25417,17 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -25518,7 +25444,7 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -25528,17 +25454,17 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -25555,7 +25481,7 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -25565,17 +25491,17 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>4,200</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -25592,7 +25518,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -25602,17 +25528,17 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>4,800</t>
+          <t>4,200</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>6.50%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -25629,7 +25555,7 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -25639,17 +25565,17 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>5,400</t>
+          <t>4,800</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>7.00%</t>
+          <t>6.50%</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -25666,7 +25592,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -25676,17 +25602,17 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>5,400</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>7.50%</t>
+          <t>7.00%</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
@@ -25703,7 +25629,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -25713,17 +25639,17 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>7.50%</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -25740,7 +25666,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -25750,17 +25676,17 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>7,200</t>
+          <t>6,600</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -25777,7 +25703,7 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -25787,17 +25713,17 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>7,800</t>
+          <t>7,200</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -25814,7 +25740,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -25824,17 +25750,17 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>9.50%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
@@ -25851,7 +25777,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -25861,17 +25787,17 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>8,400</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>9.50%</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -25888,7 +25814,7 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -25898,17 +25824,17 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>9,600</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>10.50%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -25925,7 +25851,7 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -25935,17 +25861,17 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>10,200</t>
+          <t>9,600</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>10.50%</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -25962,7 +25888,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -25972,17 +25898,17 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>10,800</t>
+          <t>10,200</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>11.50%</t>
+          <t>11.00%</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
@@ -25999,7 +25925,7 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -26009,17 +25935,17 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>11,400</t>
+          <t>10,800</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>12.00%</t>
+          <t>11.50%</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -26036,69 +25962,143 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>11,400</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>12.00%</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>MSTR</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>12,000</t>
         </is>
       </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="E75" s="11" t="inlineStr">
         <is>
           <t>6.06</t>
         </is>
       </c>
-      <c r="F74" s="11" t="inlineStr">
+      <c r="F75" s="11" t="inlineStr">
         <is>
           <t>12.50%</t>
         </is>
       </c>
-      <c r="G74" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>Pionex (派網)</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>檔位 1</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>USDT</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
         <is>
           <t>2,000,000</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr">
         <is>
           <t>50x</t>
         </is>
       </c>
-      <c r="F75" s="15" t="inlineStr">
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="G75" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Pionex (派網)</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>檔位 2</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>10,000,000</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>5x</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>180,000</t>
         </is>
       </c>
     </row>
@@ -26740,7 +26740,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>5x</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -26777,7 +26777,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>100x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
